--- a/resources/template_master_alumni.xlsx
+++ b/resources/template_master_alumni.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="12">
   <si>
     <t>nim</t>
   </si>
@@ -27,6 +27,9 @@
   </si>
   <si>
     <t>angkatan</t>
+  </si>
+  <si>
+    <t>tahun_lulus</t>
   </si>
   <si>
     <t>tanggal_lahir</t>
@@ -397,17 +400,18 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12.854" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="22.28" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="19.995" bestFit="true" customWidth="true" style="0"/>
     <col min="4" max="4" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="16.425" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="13.997" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="16.425" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -423,39 +427,45 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>4183111050</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>2020</v>
       </c>
-      <c r="E2" t="s">
-        <v>7</v>
+      <c r="E2">
+        <v>2024</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>4183111051</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3">
         <v>2021</v>
       </c>
-      <c r="E3" t="s">
-        <v>10</v>
+      <c r="F3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
